--- a/docs/45Flow-Premium-Test-Plan-macOS.xlsx
+++ b/docs/45Flow-Premium-Test-Plan-macOS.xlsx
@@ -670,7 +670,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>1. Installation (macOS)</t>
+          <t>01. Installation (macOS)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>1. Installation (macOS)</t>
+          <t>01. Installation (macOS)</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>1. Installation (macOS)</t>
+          <t>01. Installation (macOS)</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -775,7 +775,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>1. Installation (macOS)</t>
+          <t>01. Installation (macOS)</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -808,7 +808,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>1. Installation (macOS)</t>
+          <t>01. Installation (macOS)</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -844,7 +844,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>1. Installation (macOS)</t>
+          <t>01. Installation (macOS)</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -878,7 +878,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>1. Installation (macOS)</t>
+          <t>01. Installation (macOS)</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>5. Local Upload (macOS)</t>
+          <t>05. Local Upload (macOS)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>5. Local Upload (macOS)</t>
+          <t>05. Local Upload (macOS)</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -981,7 +981,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>5. Local Upload (macOS)</t>
+          <t>05. Local Upload (macOS)</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -1246,7 +1246,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2. Server Connection &amp; Auth</t>
+          <t>02. Server Connection &amp; Auth</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>2. Server Connection &amp; Auth</t>
+          <t>02. Server Connection &amp; Auth</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -1314,7 +1314,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>2. Server Connection &amp; Auth</t>
+          <t>02. Server Connection &amp; Auth</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -1349,7 +1349,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>2. Server Connection &amp; Auth</t>
+          <t>02. Server Connection &amp; Auth</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -1384,7 +1384,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2. Server Connection &amp; Auth</t>
+          <t>02. Server Connection &amp; Auth</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>2. Server Connection &amp; Auth</t>
+          <t>02. Server Connection &amp; Auth</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -1453,7 +1453,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2. Server Connection &amp; Auth</t>
+          <t>02. Server Connection &amp; Auth</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>2. Server Connection &amp; Auth</t>
+          <t>02. Server Connection &amp; Auth</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -1520,7 +1520,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2. Server Connection &amp; Auth</t>
+          <t>02. Server Connection &amp; Auth</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -1554,7 +1554,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>3. Dashboard &amp; Navigation</t>
+          <t>03. Dashboard &amp; Navigation</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>3. Dashboard &amp; Navigation</t>
+          <t>03. Dashboard &amp; Navigation</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>3. Dashboard &amp; Navigation</t>
+          <t>03. Dashboard &amp; Navigation</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -1652,7 +1652,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>4. File Share Links</t>
+          <t>04. File Share Links</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -1690,7 +1690,7 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>4. File Share Links</t>
+          <t>04. File Share Links</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -1726,7 +1726,7 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>4. File Share Links</t>
+          <t>04. File Share Links</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -1763,7 +1763,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>4. File Share Links</t>
+          <t>04. File Share Links</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>5. Local Upload</t>
+          <t>05. Local Upload</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -1839,7 +1839,7 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>5. Local Upload</t>
+          <t>05. Local Upload</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>5. Local Upload</t>
+          <t>05. Local Upload</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -1907,7 +1907,7 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>6. Upload Links</t>
+          <t>06. Upload Links</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -1943,7 +1943,7 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>6. Upload Links</t>
+          <t>06. Upload Links</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -1978,7 +1978,7 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>7. Transfer Dock</t>
+          <t>07. Transfer Dock</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -2011,7 +2011,7 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>7. Transfer Dock</t>
+          <t>07. Transfer Dock</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>7. Transfer Dock</t>
+          <t>07. Transfer Dock</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -2079,7 +2079,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>8. Managing Links</t>
+          <t>08. Managing Links</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -2112,7 +2112,7 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>8. Managing Links</t>
+          <t>08. Managing Links</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -2146,7 +2146,7 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>8. Managing Links</t>
+          <t>08. Managing Links</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -2179,7 +2179,7 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>8. Managing Links</t>
+          <t>08. Managing Links</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -2211,7 +2211,7 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>9. Video Player &amp; Review</t>
+          <t>09. Video Player &amp; Review</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -2244,7 +2244,7 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>9. Video Player &amp; Review</t>
+          <t>09. Video Player &amp; Review</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -2277,7 +2277,7 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>9. Video Player &amp; Review</t>
+          <t>09. Video Player &amp; Review</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -2313,7 +2313,7 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>9. Video Player &amp; Review</t>
+          <t>09. Video Player &amp; Review</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
